--- a/artfynd/A 50429-2021 artfynd.xlsx
+++ b/artfynd/A 50429-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119864110</v>
+        <v>119864107</v>
       </c>
       <c r="B2" t="n">
         <v>56522</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655461</v>
+        <v>655339</v>
       </c>
       <c r="R2" t="n">
-        <v>6701514</v>
+        <v>6701190</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119864070</v>
+        <v>119864109</v>
       </c>
       <c r="B3" t="n">
         <v>56522</v>
@@ -835,12 +835,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655224</v>
+        <v>655343</v>
       </c>
       <c r="R3" t="n">
-        <v>6701417</v>
+        <v>6701211</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,7 +925,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119864092</v>
+        <v>119864070</v>
       </c>
       <c r="B4" t="n">
         <v>56522</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655234</v>
+        <v>655224</v>
       </c>
       <c r="R4" t="n">
-        <v>6701262</v>
+        <v>6701417</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,7 +1050,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119864109</v>
+        <v>119864062</v>
       </c>
       <c r="B5" t="n">
         <v>56522</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655343</v>
+        <v>655452</v>
       </c>
       <c r="R5" t="n">
-        <v>6701211</v>
+        <v>6701466</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1175,7 +1175,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119864075</v>
+        <v>119864110</v>
       </c>
       <c r="B6" t="n">
         <v>56522</v>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1224,13 +1224,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655384</v>
+        <v>655461</v>
       </c>
       <c r="R6" t="n">
-        <v>6701385</v>
+        <v>6701514</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,7 +1300,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119864064</v>
+        <v>119864075</v>
       </c>
       <c r="B7" t="n">
         <v>56522</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1349,13 +1349,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655270</v>
+        <v>655384</v>
       </c>
       <c r="R7" t="n">
-        <v>6701480</v>
+        <v>6701385</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1425,7 +1425,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119864068</v>
+        <v>119864069</v>
       </c>
       <c r="B8" t="n">
         <v>56522</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1474,13 +1474,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655259</v>
+        <v>655257</v>
       </c>
       <c r="R8" t="n">
-        <v>6701362</v>
+        <v>6701371</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1550,7 +1550,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119864108</v>
+        <v>119864071</v>
       </c>
       <c r="B9" t="n">
         <v>56522</v>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655340</v>
+        <v>655225</v>
       </c>
       <c r="R9" t="n">
-        <v>6701205</v>
+        <v>6701422</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1675,7 +1675,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119864113</v>
+        <v>119864065</v>
       </c>
       <c r="B10" t="n">
         <v>56522</v>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1724,13 +1724,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655356</v>
+        <v>655359</v>
       </c>
       <c r="R10" t="n">
-        <v>6701583</v>
+        <v>6701552</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1800,7 +1800,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119864093</v>
+        <v>119864095</v>
       </c>
       <c r="B11" t="n">
         <v>56522</v>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655244</v>
+        <v>655249</v>
       </c>
       <c r="R11" t="n">
-        <v>6701306</v>
+        <v>6701328</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1925,7 +1925,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119864062</v>
+        <v>119864104</v>
       </c>
       <c r="B12" t="n">
         <v>56522</v>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1974,13 +1974,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655452</v>
+        <v>655260</v>
       </c>
       <c r="R12" t="n">
-        <v>6701466</v>
+        <v>6701155</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2175,7 +2175,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119864065</v>
+        <v>119864113</v>
       </c>
       <c r="B14" t="n">
         <v>56522</v>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -2224,13 +2224,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655359</v>
+        <v>655356</v>
       </c>
       <c r="R14" t="n">
-        <v>6701552</v>
+        <v>6701583</v>
       </c>
       <c r="S14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2300,7 +2300,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119864106</v>
+        <v>119864063</v>
       </c>
       <c r="B15" t="n">
         <v>56522</v>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2349,13 +2349,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655285</v>
+        <v>655420</v>
       </c>
       <c r="R15" t="n">
-        <v>6701220</v>
+        <v>6701457</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2425,7 +2425,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119864095</v>
+        <v>119864094</v>
       </c>
       <c r="B16" t="n">
         <v>56522</v>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655249</v>
+        <v>655248</v>
       </c>
       <c r="R16" t="n">
-        <v>6701328</v>
+        <v>6701303</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2550,7 +2550,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119864069</v>
+        <v>119864101</v>
       </c>
       <c r="B17" t="n">
         <v>56522</v>
@@ -2585,12 +2585,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2599,13 +2599,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655257</v>
+        <v>655277</v>
       </c>
       <c r="R17" t="n">
-        <v>6701371</v>
+        <v>6701424</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2675,7 +2675,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119864104</v>
+        <v>119864072</v>
       </c>
       <c r="B18" t="n">
         <v>56522</v>
@@ -2710,12 +2710,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2724,10 +2724,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655260</v>
+        <v>655235</v>
       </c>
       <c r="R18" t="n">
-        <v>6701155</v>
+        <v>6701426</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2800,7 +2800,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119864114</v>
+        <v>119864111</v>
       </c>
       <c r="B19" t="n">
         <v>56522</v>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655342</v>
+        <v>655425</v>
       </c>
       <c r="R19" t="n">
-        <v>6701610</v>
+        <v>6701494</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2925,7 +2925,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119864100</v>
+        <v>119864114</v>
       </c>
       <c r="B20" t="n">
         <v>56522</v>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2974,13 +2974,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655235</v>
+        <v>655342</v>
       </c>
       <c r="R20" t="n">
-        <v>6701434</v>
+        <v>6701610</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3050,7 +3050,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119864094</v>
+        <v>119864102</v>
       </c>
       <c r="B21" t="n">
         <v>56522</v>
@@ -3088,6 +3088,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
           <t>färsk spillning</t>
@@ -3099,10 +3104,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>655248</v>
+        <v>655288</v>
       </c>
       <c r="R21" t="n">
-        <v>6701303</v>
+        <v>6701431</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3134,7 +3139,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3144,7 +3149,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3175,7 +3180,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119864063</v>
+        <v>119864106</v>
       </c>
       <c r="B22" t="n">
         <v>56522</v>
@@ -3210,7 +3215,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -3224,13 +3229,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>655420</v>
+        <v>655285</v>
       </c>
       <c r="R22" t="n">
-        <v>6701457</v>
+        <v>6701220</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3259,7 +3264,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3269,7 +3274,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3289,7 +3294,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3300,7 +3305,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119864102</v>
+        <v>119864108</v>
       </c>
       <c r="B23" t="n">
         <v>56522</v>
@@ -3338,11 +3343,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M23" t="inlineStr">
         <is>
           <t>färsk spillning</t>
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>655288</v>
+        <v>655340</v>
       </c>
       <c r="R23" t="n">
-        <v>6701431</v>
+        <v>6701205</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3430,7 +3430,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119864101</v>
+        <v>119864105</v>
       </c>
       <c r="B24" t="n">
         <v>56522</v>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3479,13 +3479,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>655277</v>
+        <v>655283</v>
       </c>
       <c r="R24" t="n">
-        <v>6701424</v>
+        <v>6701181</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3555,7 +3555,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119864071</v>
+        <v>119864068</v>
       </c>
       <c r="B25" t="n">
         <v>56522</v>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3604,10 +3604,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>655225</v>
+        <v>655259</v>
       </c>
       <c r="R25" t="n">
-        <v>6701422</v>
+        <v>6701362</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3680,7 +3680,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119864112</v>
+        <v>119864100</v>
       </c>
       <c r="B26" t="n">
         <v>56522</v>
@@ -3729,13 +3729,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>655268</v>
+        <v>655235</v>
       </c>
       <c r="R26" t="n">
-        <v>6701452</v>
+        <v>6701434</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3805,7 +3805,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119864105</v>
+        <v>119864112</v>
       </c>
       <c r="B27" t="n">
         <v>56522</v>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3854,10 +3854,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655283</v>
+        <v>655268</v>
       </c>
       <c r="R27" t="n">
-        <v>6701181</v>
+        <v>6701452</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3930,7 +3930,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119864111</v>
+        <v>119864093</v>
       </c>
       <c r="B28" t="n">
         <v>56522</v>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655425</v>
+        <v>655244</v>
       </c>
       <c r="R28" t="n">
-        <v>6701494</v>
+        <v>6701306</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4055,7 +4055,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119864107</v>
+        <v>119864064</v>
       </c>
       <c r="B29" t="n">
         <v>56522</v>
@@ -4104,13 +4104,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655339</v>
+        <v>655270</v>
       </c>
       <c r="R29" t="n">
-        <v>6701190</v>
+        <v>6701480</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -4180,7 +4180,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119864072</v>
+        <v>119864103</v>
       </c>
       <c r="B30" t="n">
         <v>56522</v>
@@ -4215,12 +4215,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4229,10 +4229,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>655235</v>
+        <v>655247</v>
       </c>
       <c r="R30" t="n">
-        <v>6701426</v>
+        <v>6701185</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4305,7 +4305,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119864103</v>
+        <v>119864092</v>
       </c>
       <c r="B31" t="n">
         <v>56522</v>
@@ -4354,10 +4354,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>655247</v>
+        <v>655234</v>
       </c>
       <c r="R31" t="n">
-        <v>6701185</v>
+        <v>6701262</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4389,7 +4389,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 50429-2021 artfynd.xlsx
+++ b/artfynd/A 50429-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119864107</v>
+        <v>119864109</v>
       </c>
       <c r="B2" t="n">
         <v>56522</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655339</v>
+        <v>655343</v>
       </c>
       <c r="R2" t="n">
-        <v>6701190</v>
+        <v>6701211</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119864109</v>
+        <v>119864070</v>
       </c>
       <c r="B3" t="n">
         <v>56522</v>
@@ -835,12 +835,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655343</v>
+        <v>655224</v>
       </c>
       <c r="R3" t="n">
-        <v>6701211</v>
+        <v>6701417</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,7 +925,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119864070</v>
+        <v>119864062</v>
       </c>
       <c r="B4" t="n">
         <v>56522</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655224</v>
+        <v>655452</v>
       </c>
       <c r="R4" t="n">
-        <v>6701417</v>
+        <v>6701466</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1050,7 +1050,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119864062</v>
+        <v>119864107</v>
       </c>
       <c r="B5" t="n">
         <v>56522</v>
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655452</v>
+        <v>655339</v>
       </c>
       <c r="R5" t="n">
-        <v>6701466</v>
+        <v>6701190</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1550,7 +1550,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119864071</v>
+        <v>119864095</v>
       </c>
       <c r="B9" t="n">
         <v>56522</v>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655225</v>
+        <v>655249</v>
       </c>
       <c r="R9" t="n">
-        <v>6701422</v>
+        <v>6701328</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1675,7 +1675,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119864065</v>
+        <v>119864071</v>
       </c>
       <c r="B10" t="n">
         <v>56522</v>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1724,13 +1724,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655359</v>
+        <v>655225</v>
       </c>
       <c r="R10" t="n">
-        <v>6701552</v>
+        <v>6701422</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1800,7 +1800,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119864095</v>
+        <v>119864065</v>
       </c>
       <c r="B11" t="n">
         <v>56522</v>
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655249</v>
+        <v>655359</v>
       </c>
       <c r="R11" t="n">
-        <v>6701328</v>
+        <v>6701552</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -4055,7 +4055,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119864064</v>
+        <v>119864092</v>
       </c>
       <c r="B29" t="n">
         <v>56522</v>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4104,13 +4104,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655270</v>
+        <v>655234</v>
       </c>
       <c r="R29" t="n">
-        <v>6701480</v>
+        <v>6701262</v>
       </c>
       <c r="S29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
@@ -4180,7 +4180,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119864103</v>
+        <v>119864064</v>
       </c>
       <c r="B30" t="n">
         <v>56522</v>
@@ -4220,7 +4220,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>655247</v>
+        <v>655270</v>
       </c>
       <c r="R30" t="n">
-        <v>6701185</v>
+        <v>6701480</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -4305,7 +4305,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119864092</v>
+        <v>119864103</v>
       </c>
       <c r="B31" t="n">
         <v>56522</v>
@@ -4354,10 +4354,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>655234</v>
+        <v>655247</v>
       </c>
       <c r="R31" t="n">
-        <v>6701262</v>
+        <v>6701185</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4389,7 +4389,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 50429-2021 artfynd.xlsx
+++ b/artfynd/A 50429-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119864109</v>
+        <v>119864105</v>
       </c>
       <c r="B2" t="n">
         <v>56522</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655343</v>
+        <v>655283</v>
       </c>
       <c r="R2" t="n">
-        <v>6701211</v>
+        <v>6701181</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119864070</v>
+        <v>119864064</v>
       </c>
       <c r="B3" t="n">
         <v>56522</v>
@@ -835,12 +835,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,13 +849,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655224</v>
+        <v>655270</v>
       </c>
       <c r="R3" t="n">
-        <v>6701417</v>
+        <v>6701480</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -925,7 +925,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119864062</v>
+        <v>119864072</v>
       </c>
       <c r="B4" t="n">
         <v>56522</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655452</v>
+        <v>655235</v>
       </c>
       <c r="R4" t="n">
-        <v>6701466</v>
+        <v>6701426</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1050,7 +1050,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119864107</v>
+        <v>119864108</v>
       </c>
       <c r="B5" t="n">
         <v>56522</v>
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655339</v>
+        <v>655340</v>
       </c>
       <c r="R5" t="n">
-        <v>6701190</v>
+        <v>6701205</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,7 +1175,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119864110</v>
+        <v>119864104</v>
       </c>
       <c r="B6" t="n">
         <v>56522</v>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655461</v>
+        <v>655260</v>
       </c>
       <c r="R6" t="n">
-        <v>6701514</v>
+        <v>6701155</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,7 +1300,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119864075</v>
+        <v>119864110</v>
       </c>
       <c r="B7" t="n">
         <v>56522</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1349,13 +1349,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655384</v>
+        <v>655461</v>
       </c>
       <c r="R7" t="n">
-        <v>6701385</v>
+        <v>6701514</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1550,7 +1550,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119864095</v>
+        <v>119864102</v>
       </c>
       <c r="B9" t="n">
         <v>56522</v>
@@ -1588,9 +1588,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1599,10 +1604,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655249</v>
+        <v>655288</v>
       </c>
       <c r="R9" t="n">
-        <v>6701328</v>
+        <v>6701431</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1634,7 +1639,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1644,7 +1649,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1675,7 +1680,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119864071</v>
+        <v>119864111</v>
       </c>
       <c r="B10" t="n">
         <v>56522</v>
@@ -1710,7 +1715,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1724,10 +1729,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655225</v>
+        <v>655425</v>
       </c>
       <c r="R10" t="n">
-        <v>6701422</v>
+        <v>6701494</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1759,7 +1764,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1769,7 +1774,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1800,7 +1805,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119864065</v>
+        <v>119864112</v>
       </c>
       <c r="B11" t="n">
         <v>56522</v>
@@ -1835,12 +1840,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1849,13 +1854,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655359</v>
+        <v>655268</v>
       </c>
       <c r="R11" t="n">
-        <v>6701552</v>
+        <v>6701452</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1884,7 +1889,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1894,7 +1899,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1914,7 +1919,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1925,7 +1930,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119864104</v>
+        <v>119864068</v>
       </c>
       <c r="B12" t="n">
         <v>56522</v>
@@ -1960,12 +1965,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1974,10 +1979,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655260</v>
+        <v>655259</v>
       </c>
       <c r="R12" t="n">
-        <v>6701155</v>
+        <v>6701362</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -2009,7 +2014,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2019,7 +2024,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2050,7 +2055,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119864074</v>
+        <v>119864103</v>
       </c>
       <c r="B13" t="n">
         <v>56522</v>
@@ -2090,7 +2095,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2099,10 +2104,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>655245</v>
+        <v>655247</v>
       </c>
       <c r="R13" t="n">
-        <v>6701396</v>
+        <v>6701185</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2134,7 +2139,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2144,7 +2149,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2175,7 +2180,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119864113</v>
+        <v>119864095</v>
       </c>
       <c r="B14" t="n">
         <v>56522</v>
@@ -2210,12 +2215,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2224,10 +2229,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655356</v>
+        <v>655249</v>
       </c>
       <c r="R14" t="n">
-        <v>6701583</v>
+        <v>6701328</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2259,7 +2264,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2269,7 +2274,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2300,7 +2305,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119864063</v>
+        <v>119864107</v>
       </c>
       <c r="B15" t="n">
         <v>56522</v>
@@ -2349,13 +2354,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655420</v>
+        <v>655339</v>
       </c>
       <c r="R15" t="n">
-        <v>6701457</v>
+        <v>6701190</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2384,7 +2389,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2394,7 +2399,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2414,7 +2419,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2550,7 +2555,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119864101</v>
+        <v>119864114</v>
       </c>
       <c r="B17" t="n">
         <v>56522</v>
@@ -2590,7 +2595,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2599,13 +2604,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655277</v>
+        <v>655342</v>
       </c>
       <c r="R17" t="n">
-        <v>6701424</v>
+        <v>6701610</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2634,7 +2639,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2644,7 +2649,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2675,7 +2680,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119864072</v>
+        <v>119864100</v>
       </c>
       <c r="B18" t="n">
         <v>56522</v>
@@ -2710,12 +2715,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2727,10 +2732,10 @@
         <v>655235</v>
       </c>
       <c r="R18" t="n">
-        <v>6701426</v>
+        <v>6701434</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2759,7 +2764,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2769,7 +2774,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2800,7 +2805,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119864111</v>
+        <v>119864063</v>
       </c>
       <c r="B19" t="n">
         <v>56522</v>
@@ -2835,7 +2840,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2849,13 +2854,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655425</v>
+        <v>655420</v>
       </c>
       <c r="R19" t="n">
-        <v>6701494</v>
+        <v>6701457</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2884,7 +2889,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2894,7 +2899,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2914,7 +2919,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2925,7 +2930,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119864114</v>
+        <v>119864071</v>
       </c>
       <c r="B20" t="n">
         <v>56522</v>
@@ -2974,10 +2979,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655342</v>
+        <v>655225</v>
       </c>
       <c r="R20" t="n">
-        <v>6701610</v>
+        <v>6701422</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -3009,7 +3014,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3019,7 +3024,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3050,7 +3055,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119864102</v>
+        <v>119864062</v>
       </c>
       <c r="B21" t="n">
         <v>56522</v>
@@ -3088,11 +3093,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M21" t="inlineStr">
         <is>
           <t>färsk spillning</t>
@@ -3104,13 +3104,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>655288</v>
+        <v>655452</v>
       </c>
       <c r="R21" t="n">
-        <v>6701431</v>
+        <v>6701466</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3180,7 +3180,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119864106</v>
+        <v>119864065</v>
       </c>
       <c r="B22" t="n">
         <v>56522</v>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -3229,13 +3229,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>655285</v>
+        <v>655359</v>
       </c>
       <c r="R22" t="n">
-        <v>6701220</v>
+        <v>6701552</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3305,7 +3305,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119864108</v>
+        <v>119864106</v>
       </c>
       <c r="B23" t="n">
         <v>56522</v>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>655340</v>
+        <v>655285</v>
       </c>
       <c r="R23" t="n">
-        <v>6701205</v>
+        <v>6701220</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3430,7 +3430,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119864105</v>
+        <v>119864093</v>
       </c>
       <c r="B24" t="n">
         <v>56522</v>
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>655283</v>
+        <v>655244</v>
       </c>
       <c r="R24" t="n">
-        <v>6701181</v>
+        <v>6701306</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3555,7 +3555,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119864068</v>
+        <v>119864109</v>
       </c>
       <c r="B25" t="n">
         <v>56522</v>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3604,10 +3604,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>655259</v>
+        <v>655343</v>
       </c>
       <c r="R25" t="n">
-        <v>6701362</v>
+        <v>6701211</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3680,7 +3680,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119864100</v>
+        <v>119864101</v>
       </c>
       <c r="B26" t="n">
         <v>56522</v>
@@ -3729,13 +3729,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>655235</v>
+        <v>655277</v>
       </c>
       <c r="R26" t="n">
-        <v>6701434</v>
+        <v>6701424</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3805,7 +3805,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119864112</v>
+        <v>119864074</v>
       </c>
       <c r="B27" t="n">
         <v>56522</v>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3854,10 +3854,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655268</v>
+        <v>655245</v>
       </c>
       <c r="R27" t="n">
-        <v>6701452</v>
+        <v>6701396</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3930,7 +3930,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119864093</v>
+        <v>119864092</v>
       </c>
       <c r="B28" t="n">
         <v>56522</v>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655244</v>
+        <v>655234</v>
       </c>
       <c r="R28" t="n">
-        <v>6701306</v>
+        <v>6701262</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4055,7 +4055,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119864092</v>
+        <v>119864075</v>
       </c>
       <c r="B29" t="n">
         <v>56522</v>
@@ -4090,12 +4090,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4104,13 +4104,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655234</v>
+        <v>655384</v>
       </c>
       <c r="R29" t="n">
-        <v>6701262</v>
+        <v>6701385</v>
       </c>
       <c r="S29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4180,7 +4180,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119864064</v>
+        <v>119864113</v>
       </c>
       <c r="B30" t="n">
         <v>56522</v>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>655270</v>
+        <v>655356</v>
       </c>
       <c r="R30" t="n">
-        <v>6701480</v>
+        <v>6701583</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
@@ -4305,7 +4305,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119864103</v>
+        <v>119864070</v>
       </c>
       <c r="B31" t="n">
         <v>56522</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -4354,10 +4354,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>655247</v>
+        <v>655224</v>
       </c>
       <c r="R31" t="n">
-        <v>6701185</v>
+        <v>6701417</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4389,7 +4389,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 50429-2021 artfynd.xlsx
+++ b/artfynd/A 50429-2021 artfynd.xlsx
@@ -3555,7 +3555,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119864109</v>
+        <v>119864101</v>
       </c>
       <c r="B25" t="n">
         <v>56522</v>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3604,13 +3604,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>655343</v>
+        <v>655277</v>
       </c>
       <c r="R25" t="n">
-        <v>6701211</v>
+        <v>6701424</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3680,7 +3680,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119864101</v>
+        <v>119864074</v>
       </c>
       <c r="B26" t="n">
         <v>56522</v>
@@ -3720,7 +3720,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3729,13 +3729,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>655277</v>
+        <v>655245</v>
       </c>
       <c r="R26" t="n">
-        <v>6701424</v>
+        <v>6701396</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3805,7 +3805,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119864074</v>
+        <v>119864109</v>
       </c>
       <c r="B27" t="n">
         <v>56522</v>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3854,10 +3854,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655245</v>
+        <v>655343</v>
       </c>
       <c r="R27" t="n">
-        <v>6701396</v>
+        <v>6701211</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 50429-2021 artfynd.xlsx
+++ b/artfynd/A 50429-2021 artfynd.xlsx
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119864064</v>
+        <v>119864092</v>
       </c>
       <c r="B3" t="n">
         <v>56522</v>
@@ -840,7 +840,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,13 +849,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655270</v>
+        <v>655234</v>
       </c>
       <c r="R3" t="n">
-        <v>6701480</v>
+        <v>6701262</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -914,7 +914,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -925,7 +925,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119864072</v>
+        <v>119864093</v>
       </c>
       <c r="B4" t="n">
         <v>56522</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655235</v>
+        <v>655244</v>
       </c>
       <c r="R4" t="n">
-        <v>6701426</v>
+        <v>6701306</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,7 +1050,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119864108</v>
+        <v>119864103</v>
       </c>
       <c r="B5" t="n">
         <v>56522</v>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655340</v>
+        <v>655247</v>
       </c>
       <c r="R5" t="n">
-        <v>6701205</v>
+        <v>6701185</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,7 +1175,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119864104</v>
+        <v>119864112</v>
       </c>
       <c r="B6" t="n">
         <v>56522</v>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655260</v>
+        <v>655268</v>
       </c>
       <c r="R6" t="n">
-        <v>6701155</v>
+        <v>6701452</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,7 +1300,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119864110</v>
+        <v>119864108</v>
       </c>
       <c r="B7" t="n">
         <v>56522</v>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655461</v>
+        <v>655340</v>
       </c>
       <c r="R7" t="n">
-        <v>6701514</v>
+        <v>6701205</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,7 +1425,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119864069</v>
+        <v>119864110</v>
       </c>
       <c r="B8" t="n">
         <v>56522</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1474,13 +1474,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655257</v>
+        <v>655461</v>
       </c>
       <c r="R8" t="n">
-        <v>6701371</v>
+        <v>6701514</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1550,7 +1550,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119864102</v>
+        <v>119864062</v>
       </c>
       <c r="B9" t="n">
         <v>56522</v>
@@ -1588,11 +1588,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>färsk spillning</t>
@@ -1604,13 +1599,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655288</v>
+        <v>655452</v>
       </c>
       <c r="R9" t="n">
-        <v>6701431</v>
+        <v>6701466</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1639,7 +1634,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1649,7 +1644,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1669,7 +1664,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1680,7 +1675,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119864111</v>
+        <v>119864101</v>
       </c>
       <c r="B10" t="n">
         <v>56522</v>
@@ -1715,12 +1710,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1729,13 +1724,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655425</v>
+        <v>655277</v>
       </c>
       <c r="R10" t="n">
-        <v>6701494</v>
+        <v>6701424</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1764,7 +1759,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1774,7 +1769,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1805,7 +1800,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119864112</v>
+        <v>119864100</v>
       </c>
       <c r="B11" t="n">
         <v>56522</v>
@@ -1854,13 +1849,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655268</v>
+        <v>655235</v>
       </c>
       <c r="R11" t="n">
-        <v>6701452</v>
+        <v>6701434</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1889,7 +1884,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1899,7 +1894,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1930,7 +1925,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119864068</v>
+        <v>119864104</v>
       </c>
       <c r="B12" t="n">
         <v>56522</v>
@@ -1965,12 +1960,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1979,10 +1974,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655259</v>
+        <v>655260</v>
       </c>
       <c r="R12" t="n">
-        <v>6701362</v>
+        <v>6701155</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -2014,7 +2009,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2024,7 +2019,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2055,7 +2050,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119864103</v>
+        <v>119864106</v>
       </c>
       <c r="B13" t="n">
         <v>56522</v>
@@ -2090,12 +2085,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2104,10 +2099,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>655247</v>
+        <v>655285</v>
       </c>
       <c r="R13" t="n">
-        <v>6701185</v>
+        <v>6701220</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2139,7 +2134,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2149,7 +2144,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2180,7 +2175,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119864095</v>
+        <v>119864071</v>
       </c>
       <c r="B14" t="n">
         <v>56522</v>
@@ -2220,7 +2215,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2229,10 +2224,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655249</v>
+        <v>655225</v>
       </c>
       <c r="R14" t="n">
-        <v>6701328</v>
+        <v>6701422</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2264,7 +2259,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2274,7 +2269,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2430,7 +2425,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119864094</v>
+        <v>119864114</v>
       </c>
       <c r="B16" t="n">
         <v>56522</v>
@@ -2479,10 +2474,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655248</v>
+        <v>655342</v>
       </c>
       <c r="R16" t="n">
-        <v>6701303</v>
+        <v>6701610</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2514,7 +2509,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2524,7 +2519,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2555,7 +2550,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119864114</v>
+        <v>119864072</v>
       </c>
       <c r="B17" t="n">
         <v>56522</v>
@@ -2590,7 +2585,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2604,10 +2599,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655342</v>
+        <v>655235</v>
       </c>
       <c r="R17" t="n">
-        <v>6701610</v>
+        <v>6701426</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2639,7 +2634,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2649,7 +2644,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2680,7 +2675,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119864100</v>
+        <v>119864074</v>
       </c>
       <c r="B18" t="n">
         <v>56522</v>
@@ -2720,7 +2715,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2729,13 +2724,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655235</v>
+        <v>655245</v>
       </c>
       <c r="R18" t="n">
-        <v>6701434</v>
+        <v>6701396</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2764,7 +2759,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2774,7 +2769,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2805,7 +2800,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119864063</v>
+        <v>119864102</v>
       </c>
       <c r="B19" t="n">
         <v>56522</v>
@@ -2843,6 +2838,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>färsk spillning</t>
@@ -2854,13 +2854,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655420</v>
+        <v>655288</v>
       </c>
       <c r="R19" t="n">
-        <v>6701457</v>
+        <v>6701431</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2930,7 +2930,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119864071</v>
+        <v>119864111</v>
       </c>
       <c r="B20" t="n">
         <v>56522</v>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655225</v>
+        <v>655425</v>
       </c>
       <c r="R20" t="n">
-        <v>6701422</v>
+        <v>6701494</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3055,7 +3055,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119864062</v>
+        <v>119864070</v>
       </c>
       <c r="B21" t="n">
         <v>56522</v>
@@ -3090,12 +3090,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3104,13 +3104,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>655452</v>
+        <v>655224</v>
       </c>
       <c r="R21" t="n">
-        <v>6701466</v>
+        <v>6701417</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3180,7 +3180,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119864065</v>
+        <v>119864094</v>
       </c>
       <c r="B22" t="n">
         <v>56522</v>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -3229,13 +3229,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>655359</v>
+        <v>655248</v>
       </c>
       <c r="R22" t="n">
-        <v>6701552</v>
+        <v>6701303</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3305,7 +3305,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119864106</v>
+        <v>119864065</v>
       </c>
       <c r="B23" t="n">
         <v>56522</v>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -3354,13 +3354,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>655285</v>
+        <v>655359</v>
       </c>
       <c r="R23" t="n">
-        <v>6701220</v>
+        <v>6701552</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3430,7 +3430,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119864093</v>
+        <v>119864095</v>
       </c>
       <c r="B24" t="n">
         <v>56522</v>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>655244</v>
+        <v>655249</v>
       </c>
       <c r="R24" t="n">
-        <v>6701306</v>
+        <v>6701328</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3555,7 +3555,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119864101</v>
+        <v>119864068</v>
       </c>
       <c r="B25" t="n">
         <v>56522</v>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3604,13 +3604,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>655277</v>
+        <v>655259</v>
       </c>
       <c r="R25" t="n">
-        <v>6701424</v>
+        <v>6701362</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3680,7 +3680,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119864074</v>
+        <v>119864064</v>
       </c>
       <c r="B26" t="n">
         <v>56522</v>
@@ -3729,13 +3729,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>655245</v>
+        <v>655270</v>
       </c>
       <c r="R26" t="n">
-        <v>6701396</v>
+        <v>6701480</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3930,7 +3930,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119864092</v>
+        <v>119864063</v>
       </c>
       <c r="B28" t="n">
         <v>56522</v>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3979,13 +3979,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655234</v>
+        <v>655420</v>
       </c>
       <c r="R28" t="n">
-        <v>6701262</v>
+        <v>6701457</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -4180,7 +4180,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119864113</v>
+        <v>119864069</v>
       </c>
       <c r="B30" t="n">
         <v>56522</v>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>655356</v>
+        <v>655257</v>
       </c>
       <c r="R30" t="n">
-        <v>6701583</v>
+        <v>6701371</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4305,7 +4305,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119864070</v>
+        <v>119864113</v>
       </c>
       <c r="B31" t="n">
         <v>56522</v>
@@ -4340,12 +4340,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4354,10 +4354,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>655224</v>
+        <v>655356</v>
       </c>
       <c r="R31" t="n">
-        <v>6701417</v>
+        <v>6701583</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4389,7 +4389,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 50429-2021 artfynd.xlsx
+++ b/artfynd/A 50429-2021 artfynd.xlsx
@@ -2550,7 +2550,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119864072</v>
+        <v>119864074</v>
       </c>
       <c r="B17" t="n">
         <v>56522</v>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655235</v>
+        <v>655245</v>
       </c>
       <c r="R17" t="n">
-        <v>6701426</v>
+        <v>6701396</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2675,7 +2675,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119864074</v>
+        <v>119864072</v>
       </c>
       <c r="B18" t="n">
         <v>56522</v>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2724,10 +2724,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655245</v>
+        <v>655235</v>
       </c>
       <c r="R18" t="n">
-        <v>6701396</v>
+        <v>6701426</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 50429-2021 artfynd.xlsx
+++ b/artfynd/A 50429-2021 artfynd.xlsx
@@ -2550,7 +2550,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119864074</v>
+        <v>119864072</v>
       </c>
       <c r="B17" t="n">
         <v>56522</v>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2599,10 +2599,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655245</v>
+        <v>655235</v>
       </c>
       <c r="R17" t="n">
-        <v>6701396</v>
+        <v>6701426</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2634,7 +2634,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2675,7 +2675,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119864072</v>
+        <v>119864074</v>
       </c>
       <c r="B18" t="n">
         <v>56522</v>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2724,10 +2724,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655235</v>
+        <v>655245</v>
       </c>
       <c r="R18" t="n">
-        <v>6701426</v>
+        <v>6701396</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 50429-2021 artfynd.xlsx
+++ b/artfynd/A 50429-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119864105</v>
+        <v>119864062</v>
       </c>
       <c r="B2" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655283</v>
+        <v>655452</v>
       </c>
       <c r="R2" t="n">
-        <v>6701181</v>
+        <v>6701466</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -800,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119864092</v>
+        <v>119864102</v>
       </c>
       <c r="B3" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -838,9 +838,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655234</v>
+        <v>655288</v>
       </c>
       <c r="R3" t="n">
-        <v>6701262</v>
+        <v>6701431</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -884,7 +889,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +899,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +930,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119864093</v>
+        <v>119864104</v>
       </c>
       <c r="B4" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -965,7 +970,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -974,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655244</v>
+        <v>655260</v>
       </c>
       <c r="R4" t="n">
-        <v>6701306</v>
+        <v>6701155</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1009,7 +1014,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1024,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,10 +1055,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119864103</v>
+        <v>119864071</v>
       </c>
       <c r="B5" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1090,7 +1095,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1099,10 +1104,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655247</v>
+        <v>655225</v>
       </c>
       <c r="R5" t="n">
-        <v>6701185</v>
+        <v>6701422</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1134,7 +1139,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1149,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,10 +1180,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119864112</v>
+        <v>119864065</v>
       </c>
       <c r="B6" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1210,12 +1215,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1224,13 +1229,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655268</v>
+        <v>655359</v>
       </c>
       <c r="R6" t="n">
-        <v>6701452</v>
+        <v>6701552</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1259,7 +1264,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1274,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1289,7 +1294,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1300,10 +1305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119864108</v>
+        <v>119864111</v>
       </c>
       <c r="B7" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1335,7 +1340,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1349,10 +1354,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655340</v>
+        <v>655425</v>
       </c>
       <c r="R7" t="n">
-        <v>6701205</v>
+        <v>6701494</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1384,7 +1389,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1399,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,10 +1430,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119864110</v>
+        <v>119864072</v>
       </c>
       <c r="B8" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1460,7 +1465,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1474,10 +1479,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655461</v>
+        <v>655235</v>
       </c>
       <c r="R8" t="n">
-        <v>6701514</v>
+        <v>6701426</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1509,7 +1514,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1519,7 +1524,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1550,10 +1555,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119864062</v>
+        <v>119864108</v>
       </c>
       <c r="B9" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1599,13 +1604,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655452</v>
+        <v>655340</v>
       </c>
       <c r="R9" t="n">
-        <v>6701466</v>
+        <v>6701205</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1634,7 +1639,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1644,7 +1649,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1664,7 +1669,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1675,10 +1680,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119864101</v>
+        <v>119864106</v>
       </c>
       <c r="B10" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1710,12 +1715,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1724,13 +1729,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655277</v>
+        <v>655285</v>
       </c>
       <c r="R10" t="n">
-        <v>6701424</v>
+        <v>6701220</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1759,7 +1764,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1769,7 +1774,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1800,10 +1805,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119864100</v>
+        <v>119864070</v>
       </c>
       <c r="B11" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1835,7 +1840,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1849,13 +1854,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655235</v>
+        <v>655224</v>
       </c>
       <c r="R11" t="n">
-        <v>6701434</v>
+        <v>6701417</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1884,7 +1889,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1894,7 +1899,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1925,10 +1930,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119864104</v>
+        <v>119864114</v>
       </c>
       <c r="B12" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1965,7 +1970,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1974,10 +1979,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655260</v>
+        <v>655342</v>
       </c>
       <c r="R12" t="n">
-        <v>6701155</v>
+        <v>6701610</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -2009,7 +2014,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2019,7 +2024,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2050,10 +2055,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119864106</v>
+        <v>119864103</v>
       </c>
       <c r="B13" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2085,12 +2090,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2099,10 +2104,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>655285</v>
+        <v>655247</v>
       </c>
       <c r="R13" t="n">
-        <v>6701220</v>
+        <v>6701185</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2134,7 +2139,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2144,7 +2149,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2175,10 +2180,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119864071</v>
+        <v>119864095</v>
       </c>
       <c r="B14" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2215,7 +2220,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2224,10 +2229,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655225</v>
+        <v>655249</v>
       </c>
       <c r="R14" t="n">
-        <v>6701422</v>
+        <v>6701328</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2259,7 +2264,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2269,7 +2274,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2300,10 +2305,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119864107</v>
+        <v>119864113</v>
       </c>
       <c r="B15" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2335,7 +2340,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2349,13 +2354,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655339</v>
+        <v>655356</v>
       </c>
       <c r="R15" t="n">
-        <v>6701190</v>
+        <v>6701583</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2384,7 +2389,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2394,7 +2399,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2425,10 +2430,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119864114</v>
+        <v>119864107</v>
       </c>
       <c r="B16" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2474,13 +2479,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655342</v>
+        <v>655339</v>
       </c>
       <c r="R16" t="n">
-        <v>6701610</v>
+        <v>6701190</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2509,7 +2514,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2519,7 +2524,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2550,10 +2555,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119864074</v>
+        <v>119864093</v>
       </c>
       <c r="B17" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2599,10 +2604,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655245</v>
+        <v>655244</v>
       </c>
       <c r="R17" t="n">
-        <v>6701396</v>
+        <v>6701306</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2634,7 +2639,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2644,7 +2649,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2675,10 +2680,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119864072</v>
+        <v>119864068</v>
       </c>
       <c r="B18" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2710,7 +2715,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2724,10 +2729,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655235</v>
+        <v>655259</v>
       </c>
       <c r="R18" t="n">
-        <v>6701426</v>
+        <v>6701362</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2759,7 +2764,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2769,7 +2774,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2800,10 +2805,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119864102</v>
+        <v>119864074</v>
       </c>
       <c r="B19" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2838,11 +2843,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>färsk spillning</t>
@@ -2854,10 +2854,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655288</v>
+        <v>655245</v>
       </c>
       <c r="R19" t="n">
-        <v>6701431</v>
+        <v>6701396</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2930,10 +2930,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119864111</v>
+        <v>119864101</v>
       </c>
       <c r="B20" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2979,13 +2979,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655425</v>
+        <v>655277</v>
       </c>
       <c r="R20" t="n">
-        <v>6701494</v>
+        <v>6701424</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3055,10 +3055,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119864070</v>
+        <v>119864105</v>
       </c>
       <c r="B21" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3090,12 +3090,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3104,10 +3104,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>655224</v>
+        <v>655283</v>
       </c>
       <c r="R21" t="n">
-        <v>6701417</v>
+        <v>6701181</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3180,10 +3180,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119864094</v>
+        <v>119864110</v>
       </c>
       <c r="B22" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>655248</v>
+        <v>655461</v>
       </c>
       <c r="R22" t="n">
-        <v>6701303</v>
+        <v>6701514</v>
       </c>
       <c r="S22" t="n">
         <v>4</v>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3305,10 +3305,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119864065</v>
+        <v>119864092</v>
       </c>
       <c r="B23" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3340,12 +3340,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3354,13 +3354,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>655359</v>
+        <v>655234</v>
       </c>
       <c r="R23" t="n">
-        <v>6701552</v>
+        <v>6701262</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3430,10 +3430,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119864095</v>
+        <v>119864069</v>
       </c>
       <c r="B24" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3465,12 +3465,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3479,13 +3479,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>655249</v>
+        <v>655257</v>
       </c>
       <c r="R24" t="n">
-        <v>6701328</v>
+        <v>6701371</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3555,10 +3555,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119864068</v>
+        <v>119864063</v>
       </c>
       <c r="B25" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3604,13 +3604,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>655259</v>
+        <v>655420</v>
       </c>
       <c r="R25" t="n">
-        <v>6701362</v>
+        <v>6701457</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3680,10 +3680,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119864064</v>
+        <v>119864094</v>
       </c>
       <c r="B26" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3729,13 +3729,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>655270</v>
+        <v>655248</v>
       </c>
       <c r="R26" t="n">
-        <v>6701480</v>
+        <v>6701303</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3808,7 +3808,7 @@
         <v>119864109</v>
       </c>
       <c r="B27" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3930,10 +3930,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119864063</v>
+        <v>119864100</v>
       </c>
       <c r="B28" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3979,13 +3979,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655420</v>
+        <v>655235</v>
       </c>
       <c r="R28" t="n">
-        <v>6701457</v>
+        <v>6701434</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -4058,7 +4058,7 @@
         <v>119864075</v>
       </c>
       <c r="B29" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4180,10 +4180,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119864069</v>
+        <v>119864112</v>
       </c>
       <c r="B30" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4215,12 +4215,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>655257</v>
+        <v>655268</v>
       </c>
       <c r="R30" t="n">
-        <v>6701371</v>
+        <v>6701452</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4305,10 +4305,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119864113</v>
+        <v>119864064</v>
       </c>
       <c r="B31" t="n">
-        <v>56522</v>
+        <v>56532</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -4354,13 +4354,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>655356</v>
+        <v>655270</v>
       </c>
       <c r="R31" t="n">
-        <v>6701583</v>
+        <v>6701480</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">

--- a/artfynd/A 50429-2021 artfynd.xlsx
+++ b/artfynd/A 50429-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119864062</v>
+        <v>119864108</v>
       </c>
       <c r="B2" t="n">
         <v>56532</v>
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655452</v>
+        <v>655340</v>
       </c>
       <c r="R2" t="n">
-        <v>6701466</v>
+        <v>6701205</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119864102</v>
+        <v>119864100</v>
       </c>
       <c r="B3" t="n">
         <v>56532</v>
@@ -838,14 +838,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -854,13 +849,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655288</v>
+        <v>655235</v>
       </c>
       <c r="R3" t="n">
-        <v>6701431</v>
+        <v>6701434</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -889,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -899,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,7 +925,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119864104</v>
+        <v>119864110</v>
       </c>
       <c r="B4" t="n">
         <v>56532</v>
@@ -965,12 +960,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -979,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655260</v>
+        <v>655461</v>
       </c>
       <c r="R4" t="n">
-        <v>6701155</v>
+        <v>6701514</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -1014,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1024,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1055,7 +1050,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119864071</v>
+        <v>119864072</v>
       </c>
       <c r="B5" t="n">
         <v>56532</v>
@@ -1090,7 +1085,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1104,10 +1099,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655225</v>
+        <v>655235</v>
       </c>
       <c r="R5" t="n">
-        <v>6701422</v>
+        <v>6701426</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1139,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1149,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1180,7 +1175,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119864065</v>
+        <v>119864063</v>
       </c>
       <c r="B6" t="n">
         <v>56532</v>
@@ -1215,7 +1210,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1229,10 +1224,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655359</v>
+        <v>655420</v>
       </c>
       <c r="R6" t="n">
-        <v>6701552</v>
+        <v>6701457</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>
@@ -1264,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1274,7 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1305,7 +1300,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119864111</v>
+        <v>119864114</v>
       </c>
       <c r="B7" t="n">
         <v>56532</v>
@@ -1340,7 +1335,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1354,10 +1349,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655425</v>
+        <v>655342</v>
       </c>
       <c r="R7" t="n">
-        <v>6701494</v>
+        <v>6701610</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1389,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1399,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1430,7 +1425,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119864072</v>
+        <v>119864102</v>
       </c>
       <c r="B8" t="n">
         <v>56532</v>
@@ -1465,7 +1460,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655235</v>
+        <v>655288</v>
       </c>
       <c r="R8" t="n">
-        <v>6701426</v>
+        <v>6701431</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1555,7 +1555,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119864108</v>
+        <v>119864094</v>
       </c>
       <c r="B9" t="n">
         <v>56532</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655340</v>
+        <v>655248</v>
       </c>
       <c r="R9" t="n">
-        <v>6701205</v>
+        <v>6701303</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1680,7 +1680,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119864106</v>
+        <v>119864109</v>
       </c>
       <c r="B10" t="n">
         <v>56532</v>
@@ -1729,10 +1729,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655285</v>
+        <v>655343</v>
       </c>
       <c r="R10" t="n">
-        <v>6701220</v>
+        <v>6701211</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1805,7 +1805,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119864070</v>
+        <v>119864068</v>
       </c>
       <c r="B11" t="n">
         <v>56532</v>
@@ -1840,12 +1840,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1854,10 +1854,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655224</v>
+        <v>655259</v>
       </c>
       <c r="R11" t="n">
-        <v>6701417</v>
+        <v>6701362</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1930,7 +1930,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119864114</v>
+        <v>119864064</v>
       </c>
       <c r="B12" t="n">
         <v>56532</v>
@@ -1979,13 +1979,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655342</v>
+        <v>655270</v>
       </c>
       <c r="R12" t="n">
-        <v>6701610</v>
+        <v>6701480</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2055,7 +2055,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119864103</v>
+        <v>119864065</v>
       </c>
       <c r="B13" t="n">
         <v>56532</v>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2104,13 +2104,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>655247</v>
+        <v>655359</v>
       </c>
       <c r="R13" t="n">
-        <v>6701185</v>
+        <v>6701552</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2180,7 +2180,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119864095</v>
+        <v>119864105</v>
       </c>
       <c r="B14" t="n">
         <v>56532</v>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2229,10 +2229,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655249</v>
+        <v>655283</v>
       </c>
       <c r="R14" t="n">
-        <v>6701328</v>
+        <v>6701181</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2305,7 +2305,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119864113</v>
+        <v>119864104</v>
       </c>
       <c r="B15" t="n">
         <v>56532</v>
@@ -2340,12 +2340,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655356</v>
+        <v>655260</v>
       </c>
       <c r="R15" t="n">
-        <v>6701583</v>
+        <v>6701155</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2399,7 +2399,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2430,7 +2430,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119864107</v>
+        <v>119864075</v>
       </c>
       <c r="B16" t="n">
         <v>56532</v>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2479,13 +2479,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655339</v>
+        <v>655384</v>
       </c>
       <c r="R16" t="n">
-        <v>6701190</v>
+        <v>6701385</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2555,7 +2555,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119864093</v>
+        <v>119864071</v>
       </c>
       <c r="B17" t="n">
         <v>56532</v>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655244</v>
+        <v>655225</v>
       </c>
       <c r="R17" t="n">
-        <v>6701306</v>
+        <v>6701422</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2680,7 +2680,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119864068</v>
+        <v>119864111</v>
       </c>
       <c r="B18" t="n">
         <v>56532</v>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2729,10 +2729,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655259</v>
+        <v>655425</v>
       </c>
       <c r="R18" t="n">
-        <v>6701362</v>
+        <v>6701494</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2930,7 +2930,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119864101</v>
+        <v>119864107</v>
       </c>
       <c r="B20" t="n">
         <v>56532</v>
@@ -2970,7 +2970,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655277</v>
+        <v>655339</v>
       </c>
       <c r="R20" t="n">
-        <v>6701424</v>
+        <v>6701190</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3055,7 +3055,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119864105</v>
+        <v>119864062</v>
       </c>
       <c r="B21" t="n">
         <v>56532</v>
@@ -3104,13 +3104,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>655283</v>
+        <v>655452</v>
       </c>
       <c r="R21" t="n">
-        <v>6701181</v>
+        <v>6701466</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3180,7 +3180,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119864110</v>
+        <v>119864101</v>
       </c>
       <c r="B22" t="n">
         <v>56532</v>
@@ -3215,12 +3215,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3229,13 +3229,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>655461</v>
+        <v>655277</v>
       </c>
       <c r="R22" t="n">
-        <v>6701514</v>
+        <v>6701424</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3305,7 +3305,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119864092</v>
+        <v>119864093</v>
       </c>
       <c r="B23" t="n">
         <v>56532</v>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3354,10 +3354,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>655234</v>
+        <v>655244</v>
       </c>
       <c r="R23" t="n">
-        <v>6701262</v>
+        <v>6701306</v>
       </c>
       <c r="S23" t="n">
         <v>4</v>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3430,7 +3430,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119864069</v>
+        <v>119864112</v>
       </c>
       <c r="B24" t="n">
         <v>56532</v>
@@ -3465,12 +3465,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3479,13 +3479,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>655257</v>
+        <v>655268</v>
       </c>
       <c r="R24" t="n">
-        <v>6701371</v>
+        <v>6701452</v>
       </c>
       <c r="S24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3555,7 +3555,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119864063</v>
+        <v>119864103</v>
       </c>
       <c r="B25" t="n">
         <v>56532</v>
@@ -3595,7 +3595,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3604,13 +3604,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>655420</v>
+        <v>655247</v>
       </c>
       <c r="R25" t="n">
-        <v>6701457</v>
+        <v>6701185</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3680,7 +3680,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119864094</v>
+        <v>119864070</v>
       </c>
       <c r="B26" t="n">
         <v>56532</v>
@@ -3715,12 +3715,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>655248</v>
+        <v>655224</v>
       </c>
       <c r="R26" t="n">
-        <v>6701303</v>
+        <v>6701417</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3805,7 +3805,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119864109</v>
+        <v>119864069</v>
       </c>
       <c r="B27" t="n">
         <v>56532</v>
@@ -3854,13 +3854,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655343</v>
+        <v>655257</v>
       </c>
       <c r="R27" t="n">
-        <v>6701211</v>
+        <v>6701371</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3930,7 +3930,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119864100</v>
+        <v>119864106</v>
       </c>
       <c r="B28" t="n">
         <v>56532</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3979,13 +3979,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655235</v>
+        <v>655285</v>
       </c>
       <c r="R28" t="n">
-        <v>6701434</v>
+        <v>6701220</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4055,7 +4055,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119864075</v>
+        <v>119864092</v>
       </c>
       <c r="B29" t="n">
         <v>56532</v>
@@ -4090,12 +4090,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4104,13 +4104,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655384</v>
+        <v>655234</v>
       </c>
       <c r="R29" t="n">
-        <v>6701385</v>
+        <v>6701262</v>
       </c>
       <c r="S29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4180,7 +4180,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119864112</v>
+        <v>119864113</v>
       </c>
       <c r="B30" t="n">
         <v>56532</v>
@@ -4215,12 +4215,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4229,10 +4229,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>655268</v>
+        <v>655356</v>
       </c>
       <c r="R30" t="n">
-        <v>6701452</v>
+        <v>6701583</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4305,7 +4305,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119864064</v>
+        <v>119864095</v>
       </c>
       <c r="B31" t="n">
         <v>56532</v>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4354,13 +4354,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>655270</v>
+        <v>655249</v>
       </c>
       <c r="R31" t="n">
-        <v>6701480</v>
+        <v>6701328</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4389,7 +4389,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">

--- a/artfynd/A 50429-2021 artfynd.xlsx
+++ b/artfynd/A 50429-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119864108</v>
+        <v>119864071</v>
       </c>
       <c r="B2" t="n">
         <v>56532</v>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655340</v>
+        <v>655225</v>
       </c>
       <c r="R2" t="n">
-        <v>6701205</v>
+        <v>6701422</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119864100</v>
+        <v>119864068</v>
       </c>
       <c r="B3" t="n">
         <v>56532</v>
@@ -835,12 +835,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,13 +849,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655235</v>
+        <v>655259</v>
       </c>
       <c r="R3" t="n">
-        <v>6701434</v>
+        <v>6701362</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,7 +925,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119864110</v>
+        <v>119864069</v>
       </c>
       <c r="B4" t="n">
         <v>56532</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655461</v>
+        <v>655257</v>
       </c>
       <c r="R4" t="n">
-        <v>6701514</v>
+        <v>6701371</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,7 +1050,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119864072</v>
+        <v>119864064</v>
       </c>
       <c r="B5" t="n">
         <v>56532</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655235</v>
+        <v>655270</v>
       </c>
       <c r="R5" t="n">
-        <v>6701426</v>
+        <v>6701480</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1175,7 +1175,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119864063</v>
+        <v>119864114</v>
       </c>
       <c r="B6" t="n">
         <v>56532</v>
@@ -1224,13 +1224,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655420</v>
+        <v>655342</v>
       </c>
       <c r="R6" t="n">
-        <v>6701457</v>
+        <v>6701610</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1300,7 +1300,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119864114</v>
+        <v>119864107</v>
       </c>
       <c r="B7" t="n">
         <v>56532</v>
@@ -1349,13 +1349,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655342</v>
+        <v>655339</v>
       </c>
       <c r="R7" t="n">
-        <v>6701610</v>
+        <v>6701190</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,7 +1425,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119864102</v>
+        <v>119864103</v>
       </c>
       <c r="B8" t="n">
         <v>56532</v>
@@ -1463,14 +1463,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1479,10 +1474,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655288</v>
+        <v>655247</v>
       </c>
       <c r="R8" t="n">
-        <v>6701431</v>
+        <v>6701185</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1514,7 +1509,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1524,7 +1519,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1555,7 +1550,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119864094</v>
+        <v>119864112</v>
       </c>
       <c r="B9" t="n">
         <v>56532</v>
@@ -1595,7 +1590,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1604,10 +1599,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655248</v>
+        <v>655268</v>
       </c>
       <c r="R9" t="n">
-        <v>6701303</v>
+        <v>6701452</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1639,7 +1634,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1649,7 +1644,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1680,7 +1675,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119864109</v>
+        <v>119864101</v>
       </c>
       <c r="B10" t="n">
         <v>56532</v>
@@ -1715,12 +1710,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1729,13 +1724,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655343</v>
+        <v>655277</v>
       </c>
       <c r="R10" t="n">
-        <v>6701211</v>
+        <v>6701424</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1764,7 +1759,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1774,7 +1769,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1805,7 +1800,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119864068</v>
+        <v>119864113</v>
       </c>
       <c r="B11" t="n">
         <v>56532</v>
@@ -1840,7 +1835,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1854,10 +1849,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655259</v>
+        <v>655356</v>
       </c>
       <c r="R11" t="n">
-        <v>6701362</v>
+        <v>6701583</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1889,7 +1884,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1899,7 +1894,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1930,7 +1925,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119864064</v>
+        <v>119864109</v>
       </c>
       <c r="B12" t="n">
         <v>56532</v>
@@ -1965,7 +1960,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1979,13 +1974,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655270</v>
+        <v>655343</v>
       </c>
       <c r="R12" t="n">
-        <v>6701480</v>
+        <v>6701211</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2014,7 +2009,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2024,7 +2019,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2044,7 +2039,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2055,7 +2050,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119864065</v>
+        <v>119864100</v>
       </c>
       <c r="B13" t="n">
         <v>56532</v>
@@ -2090,12 +2085,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2104,13 +2099,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>655359</v>
+        <v>655235</v>
       </c>
       <c r="R13" t="n">
-        <v>6701552</v>
+        <v>6701434</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2139,7 +2134,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2149,7 +2144,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2169,7 +2164,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2180,7 +2175,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119864105</v>
+        <v>119864104</v>
       </c>
       <c r="B14" t="n">
         <v>56532</v>
@@ -2220,7 +2215,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2229,10 +2224,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655283</v>
+        <v>655260</v>
       </c>
       <c r="R14" t="n">
-        <v>6701181</v>
+        <v>6701155</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2264,7 +2259,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2274,7 +2269,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2305,7 +2300,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119864104</v>
+        <v>119864094</v>
       </c>
       <c r="B15" t="n">
         <v>56532</v>
@@ -2345,7 +2340,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2354,10 +2349,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655260</v>
+        <v>655248</v>
       </c>
       <c r="R15" t="n">
-        <v>6701155</v>
+        <v>6701303</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2389,7 +2384,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2399,7 +2394,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2430,7 +2425,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119864075</v>
+        <v>119864106</v>
       </c>
       <c r="B16" t="n">
         <v>56532</v>
@@ -2465,7 +2460,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2479,13 +2474,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655384</v>
+        <v>655285</v>
       </c>
       <c r="R16" t="n">
-        <v>6701385</v>
+        <v>6701220</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2514,7 +2509,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2524,7 +2519,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2555,7 +2550,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119864071</v>
+        <v>119864102</v>
       </c>
       <c r="B17" t="n">
         <v>56532</v>
@@ -2593,6 +2588,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
           <t>färsk spillning</t>
@@ -2604,10 +2604,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655225</v>
+        <v>655288</v>
       </c>
       <c r="R17" t="n">
-        <v>6701422</v>
+        <v>6701431</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2680,7 +2680,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119864111</v>
+        <v>119864075</v>
       </c>
       <c r="B18" t="n">
         <v>56532</v>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2729,13 +2729,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655425</v>
+        <v>655384</v>
       </c>
       <c r="R18" t="n">
-        <v>6701494</v>
+        <v>6701385</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2805,7 +2805,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119864074</v>
+        <v>119864111</v>
       </c>
       <c r="B19" t="n">
         <v>56532</v>
@@ -2840,7 +2840,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2854,10 +2854,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655245</v>
+        <v>655425</v>
       </c>
       <c r="R19" t="n">
-        <v>6701396</v>
+        <v>6701494</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2930,7 +2930,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119864107</v>
+        <v>119864062</v>
       </c>
       <c r="B20" t="n">
         <v>56532</v>
@@ -2979,13 +2979,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655339</v>
+        <v>655452</v>
       </c>
       <c r="R20" t="n">
-        <v>6701190</v>
+        <v>6701466</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -3055,7 +3055,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119864062</v>
+        <v>119864065</v>
       </c>
       <c r="B21" t="n">
         <v>56532</v>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -3104,13 +3104,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>655452</v>
+        <v>655359</v>
       </c>
       <c r="R21" t="n">
-        <v>6701466</v>
+        <v>6701552</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3180,7 +3180,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119864101</v>
+        <v>119864092</v>
       </c>
       <c r="B22" t="n">
         <v>56532</v>
@@ -3229,13 +3229,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>655277</v>
+        <v>655234</v>
       </c>
       <c r="R22" t="n">
-        <v>6701424</v>
+        <v>6701262</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3305,7 +3305,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119864093</v>
+        <v>119864063</v>
       </c>
       <c r="B23" t="n">
         <v>56532</v>
@@ -3354,13 +3354,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>655244</v>
+        <v>655420</v>
       </c>
       <c r="R23" t="n">
-        <v>6701306</v>
+        <v>6701457</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3430,7 +3430,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119864112</v>
+        <v>119864093</v>
       </c>
       <c r="B24" t="n">
         <v>56532</v>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3479,10 +3479,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>655268</v>
+        <v>655244</v>
       </c>
       <c r="R24" t="n">
-        <v>6701452</v>
+        <v>6701306</v>
       </c>
       <c r="S24" t="n">
         <v>4</v>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3555,7 +3555,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119864103</v>
+        <v>119864074</v>
       </c>
       <c r="B25" t="n">
         <v>56532</v>
@@ -3595,7 +3595,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3604,10 +3604,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>655247</v>
+        <v>655245</v>
       </c>
       <c r="R25" t="n">
-        <v>6701185</v>
+        <v>6701396</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3680,7 +3680,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119864070</v>
+        <v>119864072</v>
       </c>
       <c r="B26" t="n">
         <v>56532</v>
@@ -3715,12 +3715,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3729,10 +3729,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>655224</v>
+        <v>655235</v>
       </c>
       <c r="R26" t="n">
-        <v>6701417</v>
+        <v>6701426</v>
       </c>
       <c r="S26" t="n">
         <v>4</v>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3805,7 +3805,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119864069</v>
+        <v>119864110</v>
       </c>
       <c r="B27" t="n">
         <v>56532</v>
@@ -3840,7 +3840,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3854,13 +3854,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655257</v>
+        <v>655461</v>
       </c>
       <c r="R27" t="n">
-        <v>6701371</v>
+        <v>6701514</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3930,7 +3930,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119864106</v>
+        <v>119864095</v>
       </c>
       <c r="B28" t="n">
         <v>56532</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655285</v>
+        <v>655249</v>
       </c>
       <c r="R28" t="n">
-        <v>6701220</v>
+        <v>6701328</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4055,7 +4055,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119864092</v>
+        <v>119864108</v>
       </c>
       <c r="B29" t="n">
         <v>56532</v>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655234</v>
+        <v>655340</v>
       </c>
       <c r="R29" t="n">
-        <v>6701262</v>
+        <v>6701205</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4180,7 +4180,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119864113</v>
+        <v>119864070</v>
       </c>
       <c r="B30" t="n">
         <v>56532</v>
@@ -4215,12 +4215,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4229,10 +4229,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>655356</v>
+        <v>655224</v>
       </c>
       <c r="R30" t="n">
-        <v>6701583</v>
+        <v>6701417</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4305,7 +4305,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119864095</v>
+        <v>119864105</v>
       </c>
       <c r="B31" t="n">
         <v>56532</v>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4354,10 +4354,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>655249</v>
+        <v>655283</v>
       </c>
       <c r="R31" t="n">
-        <v>6701328</v>
+        <v>6701181</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4389,7 +4389,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 50429-2021 artfynd.xlsx
+++ b/artfynd/A 50429-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119864071</v>
+        <v>119864108</v>
       </c>
       <c r="B2" t="n">
         <v>56532</v>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655225</v>
+        <v>655340</v>
       </c>
       <c r="R2" t="n">
-        <v>6701422</v>
+        <v>6701205</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119864068</v>
+        <v>119864105</v>
       </c>
       <c r="B3" t="n">
         <v>56532</v>
@@ -835,7 +835,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655259</v>
+        <v>655283</v>
       </c>
       <c r="R3" t="n">
-        <v>6701362</v>
+        <v>6701181</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,7 +925,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119864069</v>
+        <v>119864064</v>
       </c>
       <c r="B4" t="n">
         <v>56532</v>
@@ -960,7 +960,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655257</v>
+        <v>655270</v>
       </c>
       <c r="R4" t="n">
-        <v>6701371</v>
+        <v>6701480</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1050,7 +1050,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119864064</v>
+        <v>119864063</v>
       </c>
       <c r="B5" t="n">
         <v>56532</v>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655270</v>
+        <v>655420</v>
       </c>
       <c r="R5" t="n">
-        <v>6701480</v>
+        <v>6701457</v>
       </c>
       <c r="S5" t="n">
         <v>6</v>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,7 +1175,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119864114</v>
+        <v>119864109</v>
       </c>
       <c r="B6" t="n">
         <v>56532</v>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655342</v>
+        <v>655343</v>
       </c>
       <c r="R6" t="n">
-        <v>6701610</v>
+        <v>6701211</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,7 +1300,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119864107</v>
+        <v>119864100</v>
       </c>
       <c r="B7" t="n">
         <v>56532</v>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1349,13 +1349,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655339</v>
+        <v>655235</v>
       </c>
       <c r="R7" t="n">
-        <v>6701190</v>
+        <v>6701434</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,7 +1425,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119864103</v>
+        <v>119864106</v>
       </c>
       <c r="B8" t="n">
         <v>56532</v>
@@ -1460,12 +1460,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655247</v>
+        <v>655285</v>
       </c>
       <c r="R8" t="n">
-        <v>6701185</v>
+        <v>6701220</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1550,7 +1550,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119864112</v>
+        <v>119864095</v>
       </c>
       <c r="B9" t="n">
         <v>56532</v>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655268</v>
+        <v>655249</v>
       </c>
       <c r="R9" t="n">
-        <v>6701452</v>
+        <v>6701328</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1675,7 +1675,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119864101</v>
+        <v>119864114</v>
       </c>
       <c r="B10" t="n">
         <v>56532</v>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1724,13 +1724,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655277</v>
+        <v>655342</v>
       </c>
       <c r="R10" t="n">
-        <v>6701424</v>
+        <v>6701610</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1800,7 +1800,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119864113</v>
+        <v>119864072</v>
       </c>
       <c r="B11" t="n">
         <v>56532</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1849,10 +1849,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655356</v>
+        <v>655235</v>
       </c>
       <c r="R11" t="n">
-        <v>6701583</v>
+        <v>6701426</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1925,7 +1925,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119864109</v>
+        <v>119864107</v>
       </c>
       <c r="B12" t="n">
         <v>56532</v>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1974,13 +1974,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655343</v>
+        <v>655339</v>
       </c>
       <c r="R12" t="n">
-        <v>6701211</v>
+        <v>6701190</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2050,7 +2050,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119864100</v>
+        <v>119864112</v>
       </c>
       <c r="B13" t="n">
         <v>56532</v>
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>655235</v>
+        <v>655268</v>
       </c>
       <c r="R13" t="n">
-        <v>6701434</v>
+        <v>6701452</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2175,7 +2175,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119864104</v>
+        <v>119864113</v>
       </c>
       <c r="B14" t="n">
         <v>56532</v>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655260</v>
+        <v>655356</v>
       </c>
       <c r="R14" t="n">
-        <v>6701155</v>
+        <v>6701583</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2259,7 +2259,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2300,7 +2300,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119864094</v>
+        <v>119864071</v>
       </c>
       <c r="B15" t="n">
         <v>56532</v>
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655248</v>
+        <v>655225</v>
       </c>
       <c r="R15" t="n">
-        <v>6701303</v>
+        <v>6701422</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2425,7 +2425,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119864106</v>
+        <v>119864110</v>
       </c>
       <c r="B16" t="n">
         <v>56532</v>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655285</v>
+        <v>655461</v>
       </c>
       <c r="R16" t="n">
-        <v>6701220</v>
+        <v>6701514</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2550,7 +2550,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119864102</v>
+        <v>119864075</v>
       </c>
       <c r="B17" t="n">
         <v>56532</v>
@@ -2585,12 +2585,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2604,13 +2599,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655288</v>
+        <v>655384</v>
       </c>
       <c r="R17" t="n">
-        <v>6701431</v>
+        <v>6701385</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2639,7 +2634,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2649,7 +2644,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2680,7 +2675,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119864075</v>
+        <v>119864111</v>
       </c>
       <c r="B18" t="n">
         <v>56532</v>
@@ -2715,7 +2710,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2729,13 +2724,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655384</v>
+        <v>655425</v>
       </c>
       <c r="R18" t="n">
-        <v>6701385</v>
+        <v>6701494</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2764,7 +2759,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2774,7 +2769,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2805,7 +2800,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119864111</v>
+        <v>119864094</v>
       </c>
       <c r="B19" t="n">
         <v>56532</v>
@@ -2840,7 +2835,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2854,10 +2849,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655425</v>
+        <v>655248</v>
       </c>
       <c r="R19" t="n">
-        <v>6701494</v>
+        <v>6701303</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -2889,7 +2884,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2899,7 +2894,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2930,7 +2925,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119864062</v>
+        <v>119864102</v>
       </c>
       <c r="B20" t="n">
         <v>56532</v>
@@ -2968,6 +2963,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
           <t>färsk spillning</t>
@@ -2979,13 +2979,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655452</v>
+        <v>655288</v>
       </c>
       <c r="R20" t="n">
-        <v>6701466</v>
+        <v>6701431</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -3055,7 +3055,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119864065</v>
+        <v>119864093</v>
       </c>
       <c r="B21" t="n">
         <v>56532</v>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -3104,13 +3104,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>655359</v>
+        <v>655244</v>
       </c>
       <c r="R21" t="n">
-        <v>6701552</v>
+        <v>6701306</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -3180,7 +3180,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119864092</v>
+        <v>119864062</v>
       </c>
       <c r="B22" t="n">
         <v>56532</v>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3229,13 +3229,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>655234</v>
+        <v>655452</v>
       </c>
       <c r="R22" t="n">
-        <v>6701262</v>
+        <v>6701466</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3305,7 +3305,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119864063</v>
+        <v>119864104</v>
       </c>
       <c r="B23" t="n">
         <v>56532</v>
@@ -3345,7 +3345,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3354,13 +3354,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>655420</v>
+        <v>655260</v>
       </c>
       <c r="R23" t="n">
-        <v>6701457</v>
+        <v>6701155</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3430,7 +3430,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119864093</v>
+        <v>119864101</v>
       </c>
       <c r="B24" t="n">
         <v>56532</v>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3479,13 +3479,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>655244</v>
+        <v>655277</v>
       </c>
       <c r="R24" t="n">
-        <v>6701306</v>
+        <v>6701424</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3555,7 +3555,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119864074</v>
+        <v>119864069</v>
       </c>
       <c r="B25" t="n">
         <v>56532</v>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3604,13 +3604,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>655245</v>
+        <v>655257</v>
       </c>
       <c r="R25" t="n">
-        <v>6701396</v>
+        <v>6701371</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3680,7 +3680,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119864072</v>
+        <v>119864065</v>
       </c>
       <c r="B26" t="n">
         <v>56532</v>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3729,13 +3729,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>655235</v>
+        <v>655359</v>
       </c>
       <c r="R26" t="n">
-        <v>6701426</v>
+        <v>6701552</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3805,7 +3805,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119864110</v>
+        <v>119864070</v>
       </c>
       <c r="B27" t="n">
         <v>56532</v>
@@ -3840,12 +3840,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3854,10 +3854,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655461</v>
+        <v>655224</v>
       </c>
       <c r="R27" t="n">
-        <v>6701514</v>
+        <v>6701417</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3930,7 +3930,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119864095</v>
+        <v>119864068</v>
       </c>
       <c r="B28" t="n">
         <v>56532</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3979,10 +3979,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655249</v>
+        <v>655259</v>
       </c>
       <c r="R28" t="n">
-        <v>6701328</v>
+        <v>6701362</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4055,7 +4055,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119864108</v>
+        <v>119864092</v>
       </c>
       <c r="B29" t="n">
         <v>56532</v>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655340</v>
+        <v>655234</v>
       </c>
       <c r="R29" t="n">
-        <v>6701205</v>
+        <v>6701262</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4180,7 +4180,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119864070</v>
+        <v>119864074</v>
       </c>
       <c r="B30" t="n">
         <v>56532</v>
@@ -4215,12 +4215,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4229,10 +4229,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>655224</v>
+        <v>655245</v>
       </c>
       <c r="R30" t="n">
-        <v>6701417</v>
+        <v>6701396</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4305,7 +4305,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119864105</v>
+        <v>119864103</v>
       </c>
       <c r="B31" t="n">
         <v>56532</v>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4354,10 +4354,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>655283</v>
+        <v>655247</v>
       </c>
       <c r="R31" t="n">
-        <v>6701181</v>
+        <v>6701185</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4389,7 +4389,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 50429-2021 artfynd.xlsx
+++ b/artfynd/A 50429-2021 artfynd.xlsx
@@ -800,7 +800,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119864105</v>
+        <v>119864106</v>
       </c>
       <c r="B3" t="n">
         <v>56532</v>
@@ -835,7 +835,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -849,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655283</v>
+        <v>655285</v>
       </c>
       <c r="R3" t="n">
-        <v>6701181</v>
+        <v>6701220</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,7 +925,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119864064</v>
+        <v>119864105</v>
       </c>
       <c r="B4" t="n">
         <v>56532</v>
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655270</v>
+        <v>655283</v>
       </c>
       <c r="R4" t="n">
-        <v>6701480</v>
+        <v>6701181</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1050,7 +1050,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119864063</v>
+        <v>119864072</v>
       </c>
       <c r="B5" t="n">
         <v>56532</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -1099,13 +1099,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655420</v>
+        <v>655235</v>
       </c>
       <c r="R5" t="n">
-        <v>6701457</v>
+        <v>6701426</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1175,7 +1175,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119864109</v>
+        <v>119864101</v>
       </c>
       <c r="B6" t="n">
         <v>56532</v>
@@ -1210,12 +1210,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1224,13 +1224,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655343</v>
+        <v>655277</v>
       </c>
       <c r="R6" t="n">
-        <v>6701211</v>
+        <v>6701424</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,7 +1300,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119864100</v>
+        <v>119864102</v>
       </c>
       <c r="B7" t="n">
         <v>56532</v>
@@ -1338,9 +1338,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1349,13 +1354,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655235</v>
+        <v>655288</v>
       </c>
       <c r="R7" t="n">
-        <v>6701434</v>
+        <v>6701431</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1384,7 +1389,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1394,7 +1399,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1425,7 +1430,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119864106</v>
+        <v>119864064</v>
       </c>
       <c r="B8" t="n">
         <v>56532</v>
@@ -1460,7 +1465,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1474,13 +1479,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655285</v>
+        <v>655270</v>
       </c>
       <c r="R8" t="n">
-        <v>6701220</v>
+        <v>6701480</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1509,7 +1514,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1519,7 +1524,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1539,7 +1544,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1550,7 +1555,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119864095</v>
+        <v>119864103</v>
       </c>
       <c r="B9" t="n">
         <v>56532</v>
@@ -1599,10 +1604,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655249</v>
+        <v>655247</v>
       </c>
       <c r="R9" t="n">
-        <v>6701328</v>
+        <v>6701185</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1634,7 +1639,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1644,7 +1649,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1675,7 +1680,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119864114</v>
+        <v>119864112</v>
       </c>
       <c r="B10" t="n">
         <v>56532</v>
@@ -1715,7 +1720,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1724,10 +1729,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655342</v>
+        <v>655268</v>
       </c>
       <c r="R10" t="n">
-        <v>6701610</v>
+        <v>6701452</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1759,7 +1764,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1769,7 +1774,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1800,7 +1805,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119864072</v>
+        <v>119864111</v>
       </c>
       <c r="B11" t="n">
         <v>56532</v>
@@ -1835,7 +1840,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1849,10 +1854,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655235</v>
+        <v>655425</v>
       </c>
       <c r="R11" t="n">
-        <v>6701426</v>
+        <v>6701494</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1884,7 +1889,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1894,7 +1899,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1925,7 +1930,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119864107</v>
+        <v>119864068</v>
       </c>
       <c r="B12" t="n">
         <v>56532</v>
@@ -1960,7 +1965,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1974,13 +1979,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655339</v>
+        <v>655259</v>
       </c>
       <c r="R12" t="n">
-        <v>6701190</v>
+        <v>6701362</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2009,7 +2014,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2019,7 +2024,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2050,7 +2055,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119864112</v>
+        <v>119864069</v>
       </c>
       <c r="B13" t="n">
         <v>56532</v>
@@ -2085,12 +2090,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2099,13 +2104,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>655268</v>
+        <v>655257</v>
       </c>
       <c r="R13" t="n">
-        <v>6701452</v>
+        <v>6701371</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2134,7 +2139,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2144,7 +2149,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2175,7 +2180,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119864113</v>
+        <v>119864065</v>
       </c>
       <c r="B14" t="n">
         <v>56532</v>
@@ -2210,7 +2215,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -2224,13 +2229,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655356</v>
+        <v>655359</v>
       </c>
       <c r="R14" t="n">
-        <v>6701583</v>
+        <v>6701552</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2259,7 +2264,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2269,7 +2274,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2289,7 +2294,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2300,7 +2305,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119864071</v>
+        <v>119864075</v>
       </c>
       <c r="B15" t="n">
         <v>56532</v>
@@ -2335,7 +2340,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -2349,13 +2354,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655225</v>
+        <v>655384</v>
       </c>
       <c r="R15" t="n">
-        <v>6701422</v>
+        <v>6701385</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2384,7 +2389,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2394,7 +2399,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2425,7 +2430,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119864110</v>
+        <v>119864107</v>
       </c>
       <c r="B16" t="n">
         <v>56532</v>
@@ -2460,7 +2465,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2474,13 +2479,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655461</v>
+        <v>655339</v>
       </c>
       <c r="R16" t="n">
-        <v>6701514</v>
+        <v>6701190</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2509,7 +2514,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2519,7 +2524,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2550,7 +2555,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119864075</v>
+        <v>119864093</v>
       </c>
       <c r="B17" t="n">
         <v>56532</v>
@@ -2585,7 +2590,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2599,13 +2604,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655384</v>
+        <v>655244</v>
       </c>
       <c r="R17" t="n">
-        <v>6701385</v>
+        <v>6701306</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2634,7 +2639,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2644,7 +2649,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2675,7 +2680,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119864111</v>
+        <v>119864074</v>
       </c>
       <c r="B18" t="n">
         <v>56532</v>
@@ -2710,7 +2715,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2724,10 +2729,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655425</v>
+        <v>655245</v>
       </c>
       <c r="R18" t="n">
-        <v>6701494</v>
+        <v>6701396</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2759,7 +2764,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2769,7 +2774,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2800,7 +2805,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119864094</v>
+        <v>119864063</v>
       </c>
       <c r="B19" t="n">
         <v>56532</v>
@@ -2849,13 +2854,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655248</v>
+        <v>655420</v>
       </c>
       <c r="R19" t="n">
-        <v>6701303</v>
+        <v>6701457</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2884,7 +2889,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2894,7 +2899,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2914,7 +2919,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2925,7 +2930,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119864102</v>
+        <v>119864110</v>
       </c>
       <c r="B20" t="n">
         <v>56532</v>
@@ -2960,12 +2965,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>5</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655288</v>
+        <v>655461</v>
       </c>
       <c r="R20" t="n">
-        <v>6701431</v>
+        <v>6701514</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3055,7 +3055,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119864093</v>
+        <v>119864092</v>
       </c>
       <c r="B21" t="n">
         <v>56532</v>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3104,10 +3104,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>655244</v>
+        <v>655234</v>
       </c>
       <c r="R21" t="n">
-        <v>6701306</v>
+        <v>6701262</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3180,7 +3180,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119864062</v>
+        <v>119864071</v>
       </c>
       <c r="B22" t="n">
         <v>56532</v>
@@ -3229,13 +3229,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>655452</v>
+        <v>655225</v>
       </c>
       <c r="R22" t="n">
-        <v>6701466</v>
+        <v>6701422</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -3305,7 +3305,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119864104</v>
+        <v>119864100</v>
       </c>
       <c r="B23" t="n">
         <v>56532</v>
@@ -3354,13 +3354,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>655260</v>
+        <v>655235</v>
       </c>
       <c r="R23" t="n">
-        <v>6701155</v>
+        <v>6701434</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3430,7 +3430,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119864101</v>
+        <v>119864104</v>
       </c>
       <c r="B24" t="n">
         <v>56532</v>
@@ -3479,13 +3479,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>655277</v>
+        <v>655260</v>
       </c>
       <c r="R24" t="n">
-        <v>6701424</v>
+        <v>6701155</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3555,7 +3555,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119864069</v>
+        <v>119864114</v>
       </c>
       <c r="B25" t="n">
         <v>56532</v>
@@ -3590,7 +3590,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -3604,13 +3604,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>655257</v>
+        <v>655342</v>
       </c>
       <c r="R25" t="n">
-        <v>6701371</v>
+        <v>6701610</v>
       </c>
       <c r="S25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3680,7 +3680,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119864065</v>
+        <v>119864109</v>
       </c>
       <c r="B26" t="n">
         <v>56532</v>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3729,13 +3729,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>655359</v>
+        <v>655343</v>
       </c>
       <c r="R26" t="n">
-        <v>6701552</v>
+        <v>6701211</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Signe Vendike</t>
+          <t>Carin von Köhler</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
@@ -3805,7 +3805,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119864070</v>
+        <v>119864113</v>
       </c>
       <c r="B27" t="n">
         <v>56532</v>
@@ -3840,12 +3840,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3854,10 +3854,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655224</v>
+        <v>655356</v>
       </c>
       <c r="R27" t="n">
-        <v>6701417</v>
+        <v>6701583</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3930,7 +3930,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119864068</v>
+        <v>119864062</v>
       </c>
       <c r="B28" t="n">
         <v>56532</v>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3979,13 +3979,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655259</v>
+        <v>655452</v>
       </c>
       <c r="R28" t="n">
-        <v>6701362</v>
+        <v>6701466</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Carin von Köhler</t>
+          <t>Signe Vendike</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -4055,7 +4055,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119864092</v>
+        <v>119864070</v>
       </c>
       <c r="B29" t="n">
         <v>56532</v>
@@ -4090,7 +4090,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655234</v>
+        <v>655224</v>
       </c>
       <c r="R29" t="n">
-        <v>6701262</v>
+        <v>6701417</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -4139,7 +4139,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4180,7 +4180,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119864074</v>
+        <v>119864094</v>
       </c>
       <c r="B30" t="n">
         <v>56532</v>
@@ -4229,10 +4229,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>655245</v>
+        <v>655248</v>
       </c>
       <c r="R30" t="n">
-        <v>6701396</v>
+        <v>6701303</v>
       </c>
       <c r="S30" t="n">
         <v>4</v>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4305,7 +4305,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119864103</v>
+        <v>119864095</v>
       </c>
       <c r="B31" t="n">
         <v>56532</v>
@@ -4354,10 +4354,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>655247</v>
+        <v>655249</v>
       </c>
       <c r="R31" t="n">
-        <v>6701185</v>
+        <v>6701328</v>
       </c>
       <c r="S31" t="n">
         <v>4</v>
@@ -4389,7 +4389,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD31" t="b">
